--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -55,7 +55,7 @@
     <t>blue_centers</t>
   </si>
   <si>
-    <t>micro_0068_X_II.jpg</t>
+    <t>micro_0067_X_II.jpg</t>
   </si>
   <si>
     <t>micro_0082_XI.jpg</t>
@@ -67,13 +67,13 @@
     <t>micro_0048_XLHO_O.jpg</t>
   </si>
   <si>
-    <t>micro_0070_X8.jpg</t>
+    <t>micro_0069_X8.jpg</t>
   </si>
   <si>
     <t>micro_0013_X6B.jpg</t>
   </si>
   <si>
-    <t>micro_0080_X56.jpg</t>
+    <t>micro_0079_X56.jpg</t>
   </si>
   <si>
     <t>micro_0012_X4.jpg</t>
@@ -88,10 +88,10 @@
     <t>micro_0054_HSII.jpg</t>
   </si>
   <si>
-    <t>micro_0030_SI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0035_DOQOO_SN.jpg</t>
+    <t>micro_0029_SI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0034_DOQOO_SN.jpg</t>
   </si>
   <si>
     <t>micro_0058_ISL.jpg</t>
@@ -100,10 +100,10 @@
     <t>micro_0043_S8.jpg</t>
   </si>
   <si>
-    <t>micro_0041_S6.jpg</t>
-  </si>
-  <si>
-    <t>micro_0028_S5.jpg</t>
+    <t>micro_0040_S6.jpg</t>
+  </si>
+  <si>
+    <t>micro_0027_S5.jpg</t>
   </si>
   <si>
     <t>micro_0037_S4.jpg</t>
@@ -121,22 +121,22 @@
     <t>micro_0044_D8.jpg</t>
   </si>
   <si>
-    <t>micro_0062_D7.jpg</t>
-  </si>
-  <si>
-    <t>micro_0026_D6.jpg</t>
+    <t>micro_0061_D7.jpg</t>
+  </si>
+  <si>
+    <t>micro_0082_D6.jpg</t>
   </si>
   <si>
     <t>micro_0009_D5.jpg</t>
   </si>
   <si>
-    <t>micro_0006_D4.jpg</t>
+    <t>micro_0071_D4.jpg</t>
   </si>
   <si>
     <t>micro_0025_D32.jpg</t>
   </si>
   <si>
-    <t>micro_0069_D30.jpg</t>
+    <t>micro_0068_D30.jpg</t>
   </si>
   <si>
     <t>micro_0010_D3.jpg</t>
@@ -145,43 +145,43 @@
     <t>micro_0004_D28.jpg</t>
   </si>
   <si>
-    <t>micro_0055_D27.jpg</t>
-  </si>
-  <si>
-    <t>micro_0039_D26.jpg</t>
-  </si>
-  <si>
-    <t>micro_0056_D25.jpg</t>
-  </si>
-  <si>
-    <t>micro_0038_D24.jpg</t>
+    <t>micro_0054_D27.jpg</t>
+  </si>
+  <si>
+    <t>micro_0038_D26.jpg</t>
+  </si>
+  <si>
+    <t>micro_0055_D25.jpg</t>
+  </si>
+  <si>
+    <t>micro_0037_D24.jpg</t>
   </si>
   <si>
     <t>micro_0077_D23.jpg</t>
   </si>
   <si>
-    <t>micro_0019_D22.jpg</t>
-  </si>
-  <si>
-    <t>micro_0031_D21.jpg</t>
+    <t>micro_0018_D22.jpg</t>
+  </si>
+  <si>
+    <t>micro_0030_D21.jpg</t>
   </si>
   <si>
     <t>micro_0023_0D20.jpg</t>
   </si>
   <si>
-    <t>micro_0071_D2.jpg</t>
+    <t>micro_0026_D2.jpg</t>
   </si>
   <si>
     <t>micro_0003_D19.jpg</t>
   </si>
   <si>
-    <t>micro_0022_D18.jpg</t>
-  </si>
-  <si>
-    <t>micro_0060_D17.jpg</t>
-  </si>
-  <si>
-    <t>micro_0021_D16.jpg</t>
+    <t>micro_0021_D18.jpg</t>
+  </si>
+  <si>
+    <t>micro_0033_D17.jpg</t>
+  </si>
+  <si>
+    <t>micro_0020_D16.jpg</t>
   </si>
   <si>
     <t>micro_0076_D15.jpg</t>
@@ -190,7 +190,7 @@
     <t>micro_0020_D14.jpg</t>
   </si>
   <si>
-    <t>micro_0067_D13.jpg</t>
+    <t>micro_0066_D13.jpg</t>
   </si>
   <si>
     <t>micro_0007_D12.jpg</t>
@@ -199,7 +199,7 @@
     <t>micro_0065_D11.jpg</t>
   </si>
   <si>
-    <t>micro_0045_D10.jpg</t>
+    <t>micro_0044_D10.jpg</t>
   </si>
   <si>
     <t>micro_0016_D1H.jpg</t>
@@ -742,7 +742,7 @@
         <v>63</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.9085338115692139</v>
       </c>
       <c r="D2" t="s">
         <v>113</v>
@@ -751,13 +751,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1044</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>23.96694214876033</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
         <v>114</v>
@@ -824,7 +824,7 @@
         <v>65</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.9962729811668396</v>
       </c>
       <c r="D4" t="s">
         <v>113</v>
@@ -833,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1871</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>12.79841302414666</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
         <v>114</v>
@@ -865,7 +865,7 @@
         <v>66</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.9991629719734192</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
@@ -915,13 +915,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>914</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>29.50290510006456</v>
+        <v>0</v>
       </c>
       <c r="I6" t="s">
         <v>114</v>
@@ -956,13 +956,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>32.76209677419355</v>
+        <v>0</v>
       </c>
       <c r="I7" t="s">
         <v>114</v>
@@ -988,7 +988,7 @@
         <v>69</v>
       </c>
       <c r="C8">
-        <v>0.9934314489364624</v>
+        <v>0.9903079271316528</v>
       </c>
       <c r="D8" t="s">
         <v>113</v>
@@ -997,13 +997,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1020</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>26.41802641802642</v>
+        <v>0</v>
       </c>
       <c r="I8" t="s">
         <v>114</v>
@@ -1029,7 +1029,7 @@
         <v>70</v>
       </c>
       <c r="C9">
-        <v>0.9954890012741089</v>
+        <v>0.9969092607498169</v>
       </c>
       <c r="D9" t="s">
         <v>113</v>
@@ -1038,13 +1038,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>29.41176470588236</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
         <v>114</v>
@@ -1070,7 +1070,7 @@
         <v>71</v>
       </c>
       <c r="C10">
-        <v>0.9963430166244507</v>
+        <v>0.9962290525436401</v>
       </c>
       <c r="D10" t="s">
         <v>113</v>
@@ -1079,13 +1079,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>944</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>29.20792079207921</v>
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>114</v>
@@ -1111,7 +1111,7 @@
         <v>72</v>
       </c>
       <c r="C11">
-        <v>0.445119708776474</v>
+        <v>0.9830295443534851</v>
       </c>
       <c r="D11" t="s">
         <v>113</v>
@@ -1193,7 +1193,7 @@
         <v>74</v>
       </c>
       <c r="C13">
-        <v>0.8818666338920593</v>
+        <v>0.9364910125732422</v>
       </c>
       <c r="D13" t="s">
         <v>113</v>
@@ -1202,13 +1202,13 @@
         <v>3</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>1469</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>37.57033248081841</v>
+        <v>0</v>
       </c>
       <c r="I13" t="s">
         <v>114</v>
@@ -1234,7 +1234,7 @@
         <v>75</v>
       </c>
       <c r="C14">
-        <v>0.6614634394645691</v>
+        <v>0.6378166675567627</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -1325,13 +1325,13 @@
         <v>3</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>1375</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>36.87315634218289</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
         <v>114</v>
@@ -1357,7 +1357,7 @@
         <v>78</v>
       </c>
       <c r="C17">
-        <v>0.995451807975769</v>
+        <v>0.9954283237457275</v>
       </c>
       <c r="D17" t="s">
         <v>113</v>
@@ -1366,13 +1366,13 @@
         <v>3</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>1390</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>33.6969696969697</v>
+        <v>0</v>
       </c>
       <c r="I17" t="s">
         <v>114</v>
@@ -1398,7 +1398,7 @@
         <v>79</v>
       </c>
       <c r="C18">
-        <v>0.9929208159446716</v>
+        <v>0.9940156936645508</v>
       </c>
       <c r="D18" t="s">
         <v>113</v>
@@ -1407,13 +1407,13 @@
         <v>3</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>1429</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>30.23698688108337</v>
+        <v>0</v>
       </c>
       <c r="I18" t="s">
         <v>114</v>
@@ -1448,13 +1448,13 @@
         <v>3</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>1391</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>39.8795871559633</v>
+        <v>0</v>
       </c>
       <c r="I19" t="s">
         <v>114</v>
@@ -1489,13 +1489,13 @@
         <v>3</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>1487</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>35.55714968914396</v>
+        <v>0</v>
       </c>
       <c r="I20" t="s">
         <v>114</v>
@@ -1521,7 +1521,7 @@
         <v>82</v>
       </c>
       <c r="C21">
-        <v>0.9627866744995117</v>
+        <v>0.5736554265022278</v>
       </c>
       <c r="D21" t="s">
         <v>113</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33">
         <v>1</v>

--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="114">
   <si>
     <t>filename</t>
   </si>
@@ -55,7 +55,10 @@
     <t>blue_centers</t>
   </si>
   <si>
-    <t>micro_0067_X_II.jpg</t>
+    <t>white_centers</t>
+  </si>
+  <si>
+    <t>micro_0068_X_II.jpg</t>
   </si>
   <si>
     <t>micro_0082_XI.jpg</t>
@@ -67,13 +70,13 @@
     <t>micro_0048_XLHO_O.jpg</t>
   </si>
   <si>
-    <t>micro_0069_X8.jpg</t>
+    <t>micro_0070_X8.jpg</t>
   </si>
   <si>
     <t>micro_0013_X6B.jpg</t>
   </si>
   <si>
-    <t>micro_0079_X56.jpg</t>
+    <t>micro_0080_X56.jpg</t>
   </si>
   <si>
     <t>micro_0012_X4.jpg</t>
@@ -88,22 +91,19 @@
     <t>micro_0054_HSII.jpg</t>
   </si>
   <si>
-    <t>micro_0029_SI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0034_DOQOO_SN.jpg</t>
-  </si>
-  <si>
-    <t>micro_0058_ISL.jpg</t>
+    <t>micro_0030_SI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0047_SN.jpg</t>
   </si>
   <si>
     <t>micro_0043_S8.jpg</t>
   </si>
   <si>
-    <t>micro_0040_S6.jpg</t>
-  </si>
-  <si>
-    <t>micro_0027_S5.jpg</t>
+    <t>micro_0041_S6.jpg</t>
+  </si>
+  <si>
+    <t>micro_0028_S5.jpg</t>
   </si>
   <si>
     <t>micro_0037_S4.jpg</t>
@@ -121,22 +121,22 @@
     <t>micro_0044_D8.jpg</t>
   </si>
   <si>
-    <t>micro_0061_D7.jpg</t>
-  </si>
-  <si>
-    <t>micro_0082_D6.jpg</t>
+    <t>micro_0062_D7.jpg</t>
+  </si>
+  <si>
+    <t>micro_0026_D6.jpg</t>
   </si>
   <si>
     <t>micro_0009_D5.jpg</t>
   </si>
   <si>
-    <t>micro_0071_D4.jpg</t>
+    <t>micro_0006_D4.jpg</t>
   </si>
   <si>
     <t>micro_0025_D32.jpg</t>
   </si>
   <si>
-    <t>micro_0068_D30.jpg</t>
+    <t>micro_0069_D30.jpg</t>
   </si>
   <si>
     <t>micro_0010_D3.jpg</t>
@@ -145,43 +145,43 @@
     <t>micro_0004_D28.jpg</t>
   </si>
   <si>
-    <t>micro_0054_D27.jpg</t>
-  </si>
-  <si>
-    <t>micro_0038_D26.jpg</t>
-  </si>
-  <si>
-    <t>micro_0055_D25.jpg</t>
-  </si>
-  <si>
-    <t>micro_0037_D24.jpg</t>
+    <t>micro_0055_D27.jpg</t>
+  </si>
+  <si>
+    <t>micro_0039_D26.jpg</t>
+  </si>
+  <si>
+    <t>micro_0056_D25.jpg</t>
+  </si>
+  <si>
+    <t>micro_0038_D24.jpg</t>
   </si>
   <si>
     <t>micro_0077_D23.jpg</t>
   </si>
   <si>
-    <t>micro_0018_D22.jpg</t>
-  </si>
-  <si>
-    <t>micro_0030_D21.jpg</t>
+    <t>micro_0019_D22.jpg</t>
+  </si>
+  <si>
+    <t>micro_0031_D21.jpg</t>
   </si>
   <si>
     <t>micro_0023_0D20.jpg</t>
   </si>
   <si>
-    <t>micro_0026_D2.jpg</t>
+    <t>micro_0071_D2.jpg</t>
   </si>
   <si>
     <t>micro_0003_D19.jpg</t>
   </si>
   <si>
-    <t>micro_0021_D18.jpg</t>
-  </si>
-  <si>
-    <t>micro_0033_D17.jpg</t>
-  </si>
-  <si>
-    <t>micro_0020_D16.jpg</t>
+    <t>micro_0022_D18.jpg</t>
+  </si>
+  <si>
+    <t>micro_0060_D17.jpg</t>
+  </si>
+  <si>
+    <t>micro_0021_D16.jpg</t>
   </si>
   <si>
     <t>micro_0076_D15.jpg</t>
@@ -190,7 +190,7 @@
     <t>micro_0020_D14.jpg</t>
   </si>
   <si>
-    <t>micro_0066_D13.jpg</t>
+    <t>micro_0067_D13.jpg</t>
   </si>
   <si>
     <t>micro_0007_D12.jpg</t>
@@ -199,7 +199,7 @@
     <t>micro_0065_D11.jpg</t>
   </si>
   <si>
-    <t>micro_0044_D10.jpg</t>
+    <t>micro_0045_D10.jpg</t>
   </si>
   <si>
     <t>micro_0016_D1H.jpg</t>
@@ -242,9 +242,6 @@
   </si>
   <si>
     <t>SN</t>
-  </si>
-  <si>
-    <t>SL</t>
   </si>
   <si>
     <t>S8</t>
@@ -690,10 +687,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,10 +730,13 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -745,7 +745,7 @@
         <v>0.9085338115692139</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -774,19 +774,22 @@
       <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3">
-        <v>0.8257834315299988</v>
+        <v>0.9223928451538086</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -801,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -815,10 +818,13 @@
       <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -827,7 +833,7 @@
         <v>0.9962729811668396</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -842,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -856,19 +862,22 @@
       <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5">
-        <v>0.9991629719734192</v>
+        <v>0.9988741874694824</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -883,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -897,19 +906,22 @@
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6">
-        <v>0.9814013242721558</v>
+        <v>0.8465896844863892</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -924,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -938,19 +950,22 @@
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7">
-        <v>0.9978592395782471</v>
+        <v>0.9975470900535583</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -965,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -979,19 +994,22 @@
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8">
-        <v>0.9903079271316528</v>
+        <v>0.9915710091590881</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1006,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1020,19 +1038,22 @@
       <c r="M8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9">
-        <v>0.9969092607498169</v>
+        <v>0.9963371157646179</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1047,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1061,19 +1082,22 @@
       <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10">
-        <v>0.9962290525436401</v>
+        <v>0.9974452257156372</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1088,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1102,10 +1126,13 @@
       <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
@@ -1114,7 +1141,7 @@
         <v>0.9830295443534851</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1129,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1143,19 +1170,22 @@
       <c r="M11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
       </c>
       <c r="C12">
-        <v>0.8491403460502625</v>
+        <v>0.896524965763092</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1170,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1184,19 +1214,22 @@
       <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13">
-        <v>0.9364910125732422</v>
+        <v>0.8720726370811462</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1211,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1225,19 +1258,22 @@
       <c r="M13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
         <v>75</v>
       </c>
       <c r="C14">
-        <v>0.6378166675567627</v>
+        <v>0.9960644245147705</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1252,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1266,22 +1302,25 @@
       <c r="M14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
         <v>76</v>
       </c>
       <c r="C15">
-        <v>0.9532095789909363</v>
+        <v>0.9936391115188599</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -1293,33 +1332,36 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
         <v>77</v>
       </c>
       <c r="C16">
-        <v>0.995225727558136</v>
+        <v>0.995451807975769</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1334,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1348,19 +1390,22 @@
       <c r="M16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
         <v>78</v>
       </c>
       <c r="C17">
-        <v>0.9954283237457275</v>
+        <v>0.9929208159446716</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1375,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1389,19 +1434,22 @@
       <c r="M17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
         <v>79</v>
       </c>
       <c r="C18">
-        <v>0.9940156936645508</v>
+        <v>0.9943898916244507</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1416,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1430,19 +1478,22 @@
       <c r="M18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
         <v>80</v>
       </c>
       <c r="C19">
-        <v>0.9943898916244507</v>
+        <v>0.9961403608322144</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1457,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1471,22 +1522,25 @@
       <c r="M19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
         <v>81</v>
       </c>
       <c r="C20">
-        <v>0.9961403608322144</v>
+        <v>0.9721031785011292</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -1498,13 +1552,13 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <v>1</v>
@@ -1512,19 +1566,22 @@
       <c r="M20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
         <v>82</v>
       </c>
       <c r="C21">
-        <v>0.5736554265022278</v>
+        <v>0.9951033592224121</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1539,33 +1596,36 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
         <v>83</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.9987629652023315</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1580,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1594,19 +1654,22 @@
       <c r="M22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>84</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0.9941208362579346</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1621,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1635,19 +1698,22 @@
       <c r="M23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
         <v>85</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0.9980782866477966</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1662,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1676,19 +1742,22 @@
       <c r="M24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0.9965171217918396</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1703,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1717,19 +1786,22 @@
       <c r="M25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
         <v>87</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0.9981122016906738</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1744,33 +1816,36 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
         <v>88</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.9937086701393127</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1785,33 +1860,36 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
         <v>89</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0.9984758496284485</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1826,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1840,19 +1918,22 @@
       <c r="M28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
         <v>90</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0.9957687258720398</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1867,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1881,19 +1962,22 @@
       <c r="M29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
         <v>91</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0.9995428919792175</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1908,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1922,19 +2006,22 @@
       <c r="M30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
         <v>92</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0.9988408088684082</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1949,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1963,19 +2050,22 @@
       <c r="M31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
         <v>93</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0.9990180134773254</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1990,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1999,24 +2089,27 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
         <v>94</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0.9986506104469299</v>
       </c>
       <c r="D33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2031,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2040,24 +2133,27 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
         <v>95</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0.9993026852607727</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2072,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -2086,19 +2182,22 @@
       <c r="M34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
         <v>96</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0.9992572665214539</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2113,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2127,19 +2226,22 @@
       <c r="M35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0.9992007613182068</v>
       </c>
       <c r="D36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2154,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2168,19 +2270,22 @@
       <c r="M36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
         <v>98</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0.9993838667869568</v>
       </c>
       <c r="D37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2195,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -2209,19 +2314,22 @@
       <c r="M37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
         <v>99</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0.918907105922699</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2236,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2248,21 +2356,24 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
         <v>100</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0.9977449178695679</v>
       </c>
       <c r="D39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2277,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2289,21 +2400,24 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
         <v>101</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0.9820895195007324</v>
       </c>
       <c r="D40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2318,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2332,19 +2446,22 @@
       <c r="M40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
         <v>102</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0.9996506571769714</v>
       </c>
       <c r="D41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2359,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2373,19 +2490,22 @@
       <c r="M41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
         <v>103</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0.9988899230957031</v>
       </c>
       <c r="D42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2400,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2414,19 +2534,22 @@
       <c r="M42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B43" t="s">
         <v>104</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0.9993218779563904</v>
       </c>
       <c r="D43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2441,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2455,19 +2578,22 @@
       <c r="M43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
         <v>105</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0.9883586764335632</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2482,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -2496,19 +2622,22 @@
       <c r="M44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
         <v>106</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0.9974135756492615</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2523,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -2537,19 +2666,22 @@
       <c r="M45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
         <v>107</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0.9989428520202637</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2564,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2578,19 +2710,22 @@
       <c r="M46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
         <v>108</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0.9817798137664795</v>
       </c>
       <c r="D47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2605,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -2619,19 +2754,22 @@
       <c r="M47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0.9969008564949036</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2646,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -2660,19 +2798,22 @@
       <c r="M48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B49" t="s">
         <v>110</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0.9397289156913757</v>
       </c>
       <c r="D49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2687,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -2701,19 +2842,22 @@
       <c r="M49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
         <v>111</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0.9958044290542603</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2728,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -2740,48 +2884,10 @@
         <v>0</v>
       </c>
       <c r="M50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
-      <c r="A51" t="s">
-        <v>62</v>
-      </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51" t="s">
-        <v>114</v>
-      </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1138,7 +1138,7 @@
         <v>72</v>
       </c>
       <c r="C11">
-        <v>0.9830295443534851</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>112</v>
@@ -1314,7 +1314,7 @@
         <v>76</v>
       </c>
       <c r="C15">
-        <v>0.9936391115188599</v>
+        <v>0.9914342164993286</v>
       </c>
       <c r="D15" t="s">
         <v>112</v>
@@ -1358,7 +1358,7 @@
         <v>77</v>
       </c>
       <c r="C16">
-        <v>0.995451807975769</v>
+        <v>0.9953269958496094</v>
       </c>
       <c r="D16" t="s">
         <v>112</v>
@@ -1402,7 +1402,7 @@
         <v>78</v>
       </c>
       <c r="C17">
-        <v>0.9929208159446716</v>
+        <v>0.9901033639907837</v>
       </c>
       <c r="D17" t="s">
         <v>112</v>
@@ -1446,7 +1446,7 @@
         <v>79</v>
       </c>
       <c r="C18">
-        <v>0.9943898916244507</v>
+        <v>0.9937131404876709</v>
       </c>
       <c r="D18" t="s">
         <v>112</v>
@@ -1490,7 +1490,7 @@
         <v>80</v>
       </c>
       <c r="C19">
-        <v>0.9961403608322144</v>
+        <v>0.9959126710891724</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1822,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <v>1</v>

--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -742,7 +742,7 @@
         <v>63</v>
       </c>
       <c r="C2">
-        <v>0.9085338115692139</v>
+        <v>0.8529436588287354</v>
       </c>
       <c r="D2" t="s">
         <v>112</v>
@@ -786,7 +786,7 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>0.9223928451538086</v>
+        <v>0.9099754095077515</v>
       </c>
       <c r="D3" t="s">
         <v>112</v>
@@ -830,7 +830,7 @@
         <v>65</v>
       </c>
       <c r="C4">
-        <v>0.9962729811668396</v>
+        <v>0.9964168667793274</v>
       </c>
       <c r="D4" t="s">
         <v>112</v>
@@ -874,7 +874,7 @@
         <v>66</v>
       </c>
       <c r="C5">
-        <v>0.9988741874694824</v>
+        <v>0.998839259147644</v>
       </c>
       <c r="D5" t="s">
         <v>112</v>
@@ -918,7 +918,7 @@
         <v>67</v>
       </c>
       <c r="C6">
-        <v>0.8465896844863892</v>
+        <v>0.7796013355255127</v>
       </c>
       <c r="D6" t="s">
         <v>112</v>
@@ -962,7 +962,7 @@
         <v>68</v>
       </c>
       <c r="C7">
-        <v>0.9975470900535583</v>
+        <v>0.9910327196121216</v>
       </c>
       <c r="D7" t="s">
         <v>112</v>
@@ -1006,7 +1006,7 @@
         <v>69</v>
       </c>
       <c r="C8">
-        <v>0.9915710091590881</v>
+        <v>0.9917395114898682</v>
       </c>
       <c r="D8" t="s">
         <v>112</v>
@@ -1050,7 +1050,7 @@
         <v>70</v>
       </c>
       <c r="C9">
-        <v>0.9963371157646179</v>
+        <v>0.9964473843574524</v>
       </c>
       <c r="D9" t="s">
         <v>112</v>
@@ -1094,7 +1094,7 @@
         <v>71</v>
       </c>
       <c r="C10">
-        <v>0.9974452257156372</v>
+        <v>0.9972219467163086</v>
       </c>
       <c r="D10" t="s">
         <v>112</v>
@@ -1182,7 +1182,7 @@
         <v>73</v>
       </c>
       <c r="C12">
-        <v>0.896524965763092</v>
+        <v>0.7628417015075684</v>
       </c>
       <c r="D12" t="s">
         <v>112</v>
@@ -1226,7 +1226,7 @@
         <v>74</v>
       </c>
       <c r="C13">
-        <v>0.8720726370811462</v>
+        <v>0.879502534866333</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
@@ -1270,7 +1270,7 @@
         <v>75</v>
       </c>
       <c r="C14">
-        <v>0.9960644245147705</v>
+        <v>0.9959452152252197</v>
       </c>
       <c r="D14" t="s">
         <v>112</v>
@@ -1314,7 +1314,7 @@
         <v>76</v>
       </c>
       <c r="C15">
-        <v>0.9914342164993286</v>
+        <v>0.9913234710693359</v>
       </c>
       <c r="D15" t="s">
         <v>112</v>
@@ -1358,7 +1358,7 @@
         <v>77</v>
       </c>
       <c r="C16">
-        <v>0.9953269958496094</v>
+        <v>0.9956513047218323</v>
       </c>
       <c r="D16" t="s">
         <v>112</v>
@@ -1402,7 +1402,7 @@
         <v>78</v>
       </c>
       <c r="C17">
-        <v>0.9901033639907837</v>
+        <v>0.9907405376434326</v>
       </c>
       <c r="D17" t="s">
         <v>112</v>
@@ -1446,7 +1446,7 @@
         <v>79</v>
       </c>
       <c r="C18">
-        <v>0.9937131404876709</v>
+        <v>0.9945685863494873</v>
       </c>
       <c r="D18" t="s">
         <v>112</v>
@@ -1490,7 +1490,7 @@
         <v>80</v>
       </c>
       <c r="C19">
-        <v>0.9959126710891724</v>
+        <v>0.9961426258087158</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -1534,7 +1534,7 @@
         <v>81</v>
       </c>
       <c r="C20">
-        <v>0.9721031785011292</v>
+        <v>0.939301609992981</v>
       </c>
       <c r="D20" t="s">
         <v>112</v>
@@ -1578,7 +1578,7 @@
         <v>82</v>
       </c>
       <c r="C21">
-        <v>0.9951033592224121</v>
+        <v>0.9942432641983032</v>
       </c>
       <c r="D21" t="s">
         <v>112</v>
@@ -1622,7 +1622,7 @@
         <v>83</v>
       </c>
       <c r="C22">
-        <v>0.9987629652023315</v>
+        <v>0.9989868402481079</v>
       </c>
       <c r="D22" t="s">
         <v>112</v>
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1666,7 +1666,7 @@
         <v>84</v>
       </c>
       <c r="C23">
-        <v>0.9941208362579346</v>
+        <v>0.9908839464187622</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -1710,7 +1710,7 @@
         <v>85</v>
       </c>
       <c r="C24">
-        <v>0.9980782866477966</v>
+        <v>0.9983794689178467</v>
       </c>
       <c r="D24" t="s">
         <v>112</v>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1754,7 +1754,7 @@
         <v>86</v>
       </c>
       <c r="C25">
-        <v>0.9965171217918396</v>
+        <v>0.7785727977752686</v>
       </c>
       <c r="D25" t="s">
         <v>112</v>
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1798,7 +1798,7 @@
         <v>87</v>
       </c>
       <c r="C26">
-        <v>0.9981122016906738</v>
+        <v>0.9981873035430908</v>
       </c>
       <c r="D26" t="s">
         <v>112</v>
@@ -1831,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1842,7 +1842,7 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>0.9937086701393127</v>
+        <v>0.9885565638542175</v>
       </c>
       <c r="D27" t="s">
         <v>112</v>
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1886,7 +1886,7 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>0.9984758496284485</v>
+        <v>0.9985227584838867</v>
       </c>
       <c r="D28" t="s">
         <v>112</v>
@@ -1919,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1930,7 +1930,7 @@
         <v>90</v>
       </c>
       <c r="C29">
-        <v>0.9957687258720398</v>
+        <v>0.9956930875778198</v>
       </c>
       <c r="D29" t="s">
         <v>112</v>
@@ -1963,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1974,7 +1974,7 @@
         <v>91</v>
       </c>
       <c r="C30">
-        <v>0.9995428919792175</v>
+        <v>0.999580442905426</v>
       </c>
       <c r="D30" t="s">
         <v>112</v>
@@ -2007,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2018,7 +2018,7 @@
         <v>92</v>
       </c>
       <c r="C31">
-        <v>0.9988408088684082</v>
+        <v>0.9989106059074402</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -2039,19 +2039,19 @@
         <v>113</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2062,7 +2062,7 @@
         <v>93</v>
       </c>
       <c r="C32">
-        <v>0.9990180134773254</v>
+        <v>0.9986991286277771</v>
       </c>
       <c r="D32" t="s">
         <v>112</v>
@@ -2106,7 +2106,7 @@
         <v>94</v>
       </c>
       <c r="C33">
-        <v>0.9986506104469299</v>
+        <v>0.9992579817771912</v>
       </c>
       <c r="D33" t="s">
         <v>112</v>
@@ -2139,7 +2139,7 @@
         <v>1</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2194,7 +2194,7 @@
         <v>96</v>
       </c>
       <c r="C35">
-        <v>0.9992572665214539</v>
+        <v>0.9993464350700378</v>
       </c>
       <c r="D35" t="s">
         <v>112</v>
@@ -2238,7 +2238,7 @@
         <v>97</v>
       </c>
       <c r="C36">
-        <v>0.9992007613182068</v>
+        <v>0.9991309642791748</v>
       </c>
       <c r="D36" t="s">
         <v>112</v>
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2282,7 +2282,7 @@
         <v>98</v>
       </c>
       <c r="C37">
-        <v>0.9993838667869568</v>
+        <v>0.9992704391479492</v>
       </c>
       <c r="D37" t="s">
         <v>112</v>
@@ -2326,7 +2326,7 @@
         <v>99</v>
       </c>
       <c r="C38">
-        <v>0.918907105922699</v>
+        <v>0.9898638129234314</v>
       </c>
       <c r="D38" t="s">
         <v>112</v>
@@ -2359,7 +2359,7 @@
         <v>2</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2370,7 +2370,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>0.9977449178695679</v>
+        <v>0.9971376657485962</v>
       </c>
       <c r="D39" t="s">
         <v>112</v>
@@ -2414,7 +2414,7 @@
         <v>101</v>
       </c>
       <c r="C40">
-        <v>0.9820895195007324</v>
+        <v>0.981236457824707</v>
       </c>
       <c r="D40" t="s">
         <v>112</v>
@@ -2458,7 +2458,7 @@
         <v>102</v>
       </c>
       <c r="C41">
-        <v>0.9996506571769714</v>
+        <v>0.9996522068977356</v>
       </c>
       <c r="D41" t="s">
         <v>112</v>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2502,7 +2502,7 @@
         <v>103</v>
       </c>
       <c r="C42">
-        <v>0.9988899230957031</v>
+        <v>0.9989044070243835</v>
       </c>
       <c r="D42" t="s">
         <v>112</v>
@@ -2546,7 +2546,7 @@
         <v>104</v>
       </c>
       <c r="C43">
-        <v>0.9993218779563904</v>
+        <v>0.9993866086006165</v>
       </c>
       <c r="D43" t="s">
         <v>112</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>105</v>
       </c>
       <c r="C44">
-        <v>0.9883586764335632</v>
+        <v>0.9865573048591614</v>
       </c>
       <c r="D44" t="s">
         <v>112</v>
@@ -2634,7 +2634,7 @@
         <v>106</v>
       </c>
       <c r="C45">
-        <v>0.9974135756492615</v>
+        <v>0.9975883960723877</v>
       </c>
       <c r="D45" t="s">
         <v>112</v>
@@ -2678,7 +2678,7 @@
         <v>107</v>
       </c>
       <c r="C46">
-        <v>0.9989428520202637</v>
+        <v>0.9988886713981628</v>
       </c>
       <c r="D46" t="s">
         <v>112</v>
@@ -2722,7 +2722,7 @@
         <v>108</v>
       </c>
       <c r="C47">
-        <v>0.9817798137664795</v>
+        <v>0.9835829734802246</v>
       </c>
       <c r="D47" t="s">
         <v>112</v>
@@ -2755,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2766,7 +2766,7 @@
         <v>109</v>
       </c>
       <c r="C48">
-        <v>0.9969008564949036</v>
+        <v>0.996749222278595</v>
       </c>
       <c r="D48" t="s">
         <v>112</v>
@@ -2810,7 +2810,7 @@
         <v>110</v>
       </c>
       <c r="C49">
-        <v>0.9397289156913757</v>
+        <v>0.9340880513191223</v>
       </c>
       <c r="D49" t="s">
         <v>112</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2854,7 +2854,7 @@
         <v>111</v>
       </c>
       <c r="C50">
-        <v>0.9958044290542603</v>
+        <v>0.9959298372268677</v>
       </c>
       <c r="D50" t="s">
         <v>112</v>

--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -1578,7 +1578,7 @@
         <v>82</v>
       </c>
       <c r="C21">
-        <v>0.9951033592224121</v>
+        <v>0.9942432641983032</v>
       </c>
       <c r="D21" t="s">
         <v>112</v>
@@ -1622,7 +1622,7 @@
         <v>83</v>
       </c>
       <c r="C22">
-        <v>0.9987629652023315</v>
+        <v>0.9989868402481079</v>
       </c>
       <c r="D22" t="s">
         <v>112</v>
@@ -1655,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1666,7 +1666,7 @@
         <v>84</v>
       </c>
       <c r="C23">
-        <v>0.9941208362579346</v>
+        <v>0.9908839464187622</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -1710,7 +1710,7 @@
         <v>85</v>
       </c>
       <c r="C24">
-        <v>0.9980782866477966</v>
+        <v>0.9983794689178467</v>
       </c>
       <c r="D24" t="s">
         <v>112</v>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1754,7 +1754,7 @@
         <v>86</v>
       </c>
       <c r="C25">
-        <v>0.9965171217918396</v>
+        <v>0.7785727977752686</v>
       </c>
       <c r="D25" t="s">
         <v>112</v>
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1831,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1842,7 +1842,7 @@
         <v>88</v>
       </c>
       <c r="C27">
-        <v>0.9937086701393127</v>
+        <v>0.9885565638542175</v>
       </c>
       <c r="D27" t="s">
         <v>112</v>
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1886,7 +1886,7 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>0.9984758496284485</v>
+        <v>0.9985227584838867</v>
       </c>
       <c r="D28" t="s">
         <v>112</v>
@@ -1919,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1930,7 +1930,7 @@
         <v>90</v>
       </c>
       <c r="C29">
-        <v>0.9957687258720398</v>
+        <v>0.9956930875778198</v>
       </c>
       <c r="D29" t="s">
         <v>112</v>
@@ -1963,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1974,7 +1974,7 @@
         <v>91</v>
       </c>
       <c r="C30">
-        <v>0.9995428919792175</v>
+        <v>0.999580442905426</v>
       </c>
       <c r="D30" t="s">
         <v>112</v>
@@ -2007,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2018,7 +2018,7 @@
         <v>92</v>
       </c>
       <c r="C31">
-        <v>0.9988408088684082</v>
+        <v>0.9989106059074402</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -2039,19 +2039,19 @@
         <v>113</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2106,7 +2106,7 @@
         <v>94</v>
       </c>
       <c r="C33">
-        <v>0.9986506104469299</v>
+        <v>0.9992579817771912</v>
       </c>
       <c r="D33" t="s">
         <v>112</v>
@@ -2139,7 +2139,7 @@
         <v>1</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2194,7 +2194,7 @@
         <v>96</v>
       </c>
       <c r="C35">
-        <v>0.9992572665214539</v>
+        <v>0.9993464350700378</v>
       </c>
       <c r="D35" t="s">
         <v>112</v>
@@ -2238,7 +2238,7 @@
         <v>97</v>
       </c>
       <c r="C36">
-        <v>0.9992007613182068</v>
+        <v>0.9991309642791748</v>
       </c>
       <c r="D36" t="s">
         <v>112</v>
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2282,7 +2282,7 @@
         <v>98</v>
       </c>
       <c r="C37">
-        <v>0.9993838667869568</v>
+        <v>0.9992704391479492</v>
       </c>
       <c r="D37" t="s">
         <v>112</v>
@@ -2326,7 +2326,7 @@
         <v>99</v>
       </c>
       <c r="C38">
-        <v>0.918907105922699</v>
+        <v>0.9898638129234314</v>
       </c>
       <c r="D38" t="s">
         <v>112</v>
@@ -2359,7 +2359,7 @@
         <v>2</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2370,7 +2370,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>0.9977449178695679</v>
+        <v>0.9971376657485962</v>
       </c>
       <c r="D39" t="s">
         <v>112</v>
@@ -2414,7 +2414,7 @@
         <v>101</v>
       </c>
       <c r="C40">
-        <v>0.9820895195007324</v>
+        <v>0.981236457824707</v>
       </c>
       <c r="D40" t="s">
         <v>112</v>
@@ -2458,7 +2458,7 @@
         <v>102</v>
       </c>
       <c r="C41">
-        <v>0.9996506571769714</v>
+        <v>0.9996522068977356</v>
       </c>
       <c r="D41" t="s">
         <v>112</v>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2502,7 +2502,7 @@
         <v>103</v>
       </c>
       <c r="C42">
-        <v>0.9988899230957031</v>
+        <v>0.9989044070243835</v>
       </c>
       <c r="D42" t="s">
         <v>112</v>
@@ -2546,7 +2546,7 @@
         <v>104</v>
       </c>
       <c r="C43">
-        <v>0.9993218779563904</v>
+        <v>0.9993866086006165</v>
       </c>
       <c r="D43" t="s">
         <v>112</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>105</v>
       </c>
       <c r="C44">
-        <v>0.9883586764335632</v>
+        <v>0.9865573048591614</v>
       </c>
       <c r="D44" t="s">
         <v>112</v>
@@ -2634,7 +2634,7 @@
         <v>106</v>
       </c>
       <c r="C45">
-        <v>0.9974135756492615</v>
+        <v>0.9975883960723877</v>
       </c>
       <c r="D45" t="s">
         <v>112</v>
@@ -2678,7 +2678,7 @@
         <v>107</v>
       </c>
       <c r="C46">
-        <v>0.9989428520202637</v>
+        <v>0.9988886713981628</v>
       </c>
       <c r="D46" t="s">
         <v>112</v>
@@ -2722,7 +2722,7 @@
         <v>108</v>
       </c>
       <c r="C47">
-        <v>0.9817798137664795</v>
+        <v>0.9835829734802246</v>
       </c>
       <c r="D47" t="s">
         <v>112</v>
@@ -2755,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2766,7 +2766,7 @@
         <v>109</v>
       </c>
       <c r="C48">
-        <v>0.9969008564949036</v>
+        <v>0.996749222278595</v>
       </c>
       <c r="D48" t="s">
         <v>112</v>
@@ -2810,7 +2810,7 @@
         <v>110</v>
       </c>
       <c r="C49">
-        <v>0.9397289156913757</v>
+        <v>0.9340880513191223</v>
       </c>
       <c r="D49" t="s">
         <v>112</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:14">

--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="116">
   <si>
     <t>filename</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>white_centers</t>
+  </si>
+  <si>
+    <t>is_tri</t>
+  </si>
+  <si>
+    <t>is_double</t>
   </si>
   <si>
     <t>micro_0068_X_II.jpg</t>
@@ -687,10 +693,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,19 +739,25 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2">
         <v>0.9085338115692139</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -760,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -777,19 +789,25 @@
       <c r="N2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>0.9223928451538086</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -804,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -821,19 +839,25 @@
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>0.9962729811668396</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -848,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -865,19 +889,25 @@
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>0.9988741874694824</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -892,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -909,19 +939,25 @@
       <c r="N5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>0.8465896844863892</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -936,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -953,19 +989,25 @@
       <c r="N6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>0.9975470900535583</v>
+        <v>0.9913955926895142</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -980,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -997,19 +1039,25 @@
       <c r="N7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>0.9915710091590881</v>
+        <v>0.9273802042007446</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1024,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1041,19 +1089,25 @@
       <c r="N8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9">
         <v>0.9963371157646179</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1068,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1085,19 +1139,25 @@
       <c r="N9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10">
-        <v>0.9974452257156372</v>
+        <v>0.9976203441619873</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1112,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1129,19 +1189,25 @@
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1156,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1173,19 +1239,25 @@
       <c r="N11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>0.896524965763092</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1200,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1217,19 +1289,25 @@
       <c r="N12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13">
         <v>0.8720726370811462</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1244,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1261,19 +1339,25 @@
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <v>0.9960644245147705</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1288,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1305,19 +1389,25 @@
       <c r="N14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>0.9914342164993286</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1332,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1349,19 +1439,25 @@
       <c r="N15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16">
         <v>0.9953269958496094</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1376,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1393,19 +1489,25 @@
       <c r="N16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17">
         <v>0.9901033639907837</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1420,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1437,19 +1539,25 @@
       <c r="N17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18">
         <v>0.9937131404876709</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1464,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1481,19 +1589,25 @@
       <c r="N18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C19">
         <v>0.9959126710891724</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1508,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1525,19 +1639,25 @@
       <c r="N19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>0.9721031785011292</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1552,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1569,19 +1689,25 @@
       <c r="N20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21">
         <v>0.9942432641983032</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1596,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1613,19 +1739,25 @@
       <c r="N21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22">
         <v>0.9989868402481079</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1640,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1657,19 +1789,25 @@
       <c r="N22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C23">
         <v>0.9908839464187622</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1684,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1701,19 +1839,25 @@
       <c r="N23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <v>0.9983794689178467</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1728,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1745,19 +1889,25 @@
       <c r="N24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>0.7785727977752686</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1772,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1789,19 +1939,25 @@
       <c r="N25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>0.9981122016906738</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1816,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1833,19 +1989,25 @@
       <c r="N26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <v>0.9885565638542175</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1860,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1877,19 +2039,25 @@
       <c r="N27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>0.9985227584838867</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1904,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1921,19 +2089,25 @@
       <c r="N28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29">
         <v>0.9956930875778198</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1948,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1965,19 +2139,25 @@
       <c r="N29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C30">
         <v>0.999580442905426</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1992,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2009,19 +2189,25 @@
       <c r="N30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C31">
         <v>0.9989106059074402</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2036,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2053,19 +2239,25 @@
       <c r="N31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C32">
         <v>0.9990180134773254</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2080,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -2097,19 +2289,25 @@
       <c r="N32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C33">
         <v>0.9992579817771912</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2124,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2141,19 +2339,25 @@
       <c r="N33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C34">
         <v>0.9993026852607727</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2168,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -2185,19 +2389,25 @@
       <c r="N34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C35">
         <v>0.9993464350700378</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2212,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2229,19 +2439,25 @@
       <c r="N35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C36">
         <v>0.9991309642791748</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2256,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2273,19 +2489,25 @@
       <c r="N36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>0.9992704391479492</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2300,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -2317,19 +2539,25 @@
       <c r="N37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C38">
         <v>0.9898638129234314</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2344,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2361,19 +2589,25 @@
       <c r="N38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C39">
         <v>0.9971376657485962</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2388,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2405,19 +2639,25 @@
       <c r="N39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C40">
         <v>0.981236457824707</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2432,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2449,19 +2689,25 @@
       <c r="N40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C41">
         <v>0.9996522068977356</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2476,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2493,19 +2739,25 @@
       <c r="N41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C42">
         <v>0.9989044070243835</v>
       </c>
       <c r="D42" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2520,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2537,19 +2789,25 @@
       <c r="N42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C43">
         <v>0.9993866086006165</v>
       </c>
       <c r="D43" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2564,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2581,19 +2839,25 @@
       <c r="N43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C44">
         <v>0.9865573048591614</v>
       </c>
       <c r="D44" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2608,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -2625,19 +2889,25 @@
       <c r="N44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C45">
         <v>0.9975883960723877</v>
       </c>
       <c r="D45" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2652,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -2669,19 +2939,25 @@
       <c r="N45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C46">
         <v>0.9988886713981628</v>
       </c>
       <c r="D46" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2696,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2713,19 +2989,25 @@
       <c r="N46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C47">
         <v>0.9835829734802246</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2740,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -2757,63 +3039,75 @@
       <c r="N47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C48">
         <v>0.996749222278595</v>
       </c>
       <c r="D48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>115</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" t="s">
         <v>112</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48" t="s">
-        <v>113</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-      <c r="N48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" t="s">
-        <v>110</v>
       </c>
       <c r="C49">
         <v>0.9340880513191223</v>
       </c>
       <c r="D49" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2828,36 +3122,42 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
+        <v>115</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
         <v>113</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" t="s">
-        <v>111</v>
       </c>
       <c r="C50">
         <v>0.9958044290542603</v>
       </c>
       <c r="D50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2872,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2888,6 +3188,12 @@
       </c>
       <c r="N50">
         <v>1</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -64,151 +64,151 @@
     <t>is_double</t>
   </si>
   <si>
-    <t>micro_0068_X_II.jpg</t>
-  </si>
-  <si>
-    <t>micro_0082_XI.jpg</t>
+    <t>micro_0012_XII.jpg</t>
+  </si>
+  <si>
+    <t>micro_0094_XI.jpg</t>
   </si>
   <si>
     <t>micro_0008_XN.jpg</t>
   </si>
   <si>
-    <t>micro_0048_XLHO_O.jpg</t>
-  </si>
-  <si>
-    <t>micro_0070_X8.jpg</t>
-  </si>
-  <si>
-    <t>micro_0013_X6B.jpg</t>
-  </si>
-  <si>
-    <t>micro_0080_X56.jpg</t>
-  </si>
-  <si>
-    <t>micro_0012_X4.jpg</t>
-  </si>
-  <si>
-    <t>micro_0081_X3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0057_X_0_2460_Q00.jpg</t>
-  </si>
-  <si>
-    <t>micro_0054_HSII.jpg</t>
-  </si>
-  <si>
-    <t>micro_0030_SI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0047_SN.jpg</t>
-  </si>
-  <si>
-    <t>micro_0043_S8.jpg</t>
-  </si>
-  <si>
-    <t>micro_0041_S6.jpg</t>
-  </si>
-  <si>
-    <t>micro_0028_S5.jpg</t>
-  </si>
-  <si>
-    <t>micro_0037_S4.jpg</t>
-  </si>
-  <si>
-    <t>micro_0029_S3.jpg</t>
-  </si>
-  <si>
-    <t>micro_0073_0OQOO_S.jpg</t>
-  </si>
-  <si>
-    <t>micro_0064_D9.jpg</t>
-  </si>
-  <si>
-    <t>micro_0044_D8.jpg</t>
-  </si>
-  <si>
-    <t>micro_0062_D7.jpg</t>
-  </si>
-  <si>
-    <t>micro_0026_D6.jpg</t>
-  </si>
-  <si>
-    <t>micro_0009_D5.jpg</t>
+    <t>micro_0054_XLHO_O.jpg</t>
+  </si>
+  <si>
+    <t>micro_0081_X8.jpg</t>
+  </si>
+  <si>
+    <t>micro_0014_X6B.jpg</t>
+  </si>
+  <si>
+    <t>micro_0095_X5.jpg</t>
+  </si>
+  <si>
+    <t>micro_0013_X4.jpg</t>
+  </si>
+  <si>
+    <t>micro_0093_X3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0068_X.jpg</t>
+  </si>
+  <si>
+    <t>micro_0063_HSII.jpg</t>
+  </si>
+  <si>
+    <t>micro_0034_SI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0041_SN.jpg</t>
+  </si>
+  <si>
+    <t>micro_0048_S8.jpg</t>
+  </si>
+  <si>
+    <t>micro_0046_S6.jpg</t>
+  </si>
+  <si>
+    <t>micro_0032_S5.jpg</t>
+  </si>
+  <si>
+    <t>micro_0042_S4.jpg</t>
+  </si>
+  <si>
+    <t>micro_0033_S3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0085_S.jpg</t>
+  </si>
+  <si>
+    <t>micro_0075_D9.jpg</t>
+  </si>
+  <si>
+    <t>micro_0097_D8.jpg</t>
+  </si>
+  <si>
+    <t>micro_0090_D7.jpg</t>
+  </si>
+  <si>
+    <t>micro_0030_D6.jpg</t>
+  </si>
+  <si>
+    <t>micro_0011_D5.jpg</t>
   </si>
   <si>
     <t>micro_0006_D4.jpg</t>
   </si>
   <si>
-    <t>micro_0025_D32.jpg</t>
-  </si>
-  <si>
-    <t>micro_0069_D30.jpg</t>
-  </si>
-  <si>
-    <t>micro_0010_D3.jpg</t>
+    <t>micro_0029_D32.jpg</t>
+  </si>
+  <si>
+    <t>micro_0028_D30.jpg</t>
+  </si>
+  <si>
+    <t>micro_0045_D3.jpg</t>
   </si>
   <si>
     <t>micro_0004_D28.jpg</t>
   </si>
   <si>
-    <t>micro_0055_D27.jpg</t>
-  </si>
-  <si>
-    <t>micro_0039_D26.jpg</t>
-  </si>
-  <si>
-    <t>micro_0056_D25.jpg</t>
-  </si>
-  <si>
-    <t>micro_0038_D24.jpg</t>
-  </si>
-  <si>
-    <t>micro_0077_D23.jpg</t>
-  </si>
-  <si>
-    <t>micro_0019_D22.jpg</t>
-  </si>
-  <si>
-    <t>micro_0031_D21.jpg</t>
-  </si>
-  <si>
-    <t>micro_0023_0D20.jpg</t>
-  </si>
-  <si>
-    <t>micro_0071_D2.jpg</t>
-  </si>
-  <si>
-    <t>micro_0003_D19.jpg</t>
-  </si>
-  <si>
-    <t>micro_0022_D18.jpg</t>
-  </si>
-  <si>
-    <t>micro_0060_D17.jpg</t>
-  </si>
-  <si>
-    <t>micro_0021_D16.jpg</t>
-  </si>
-  <si>
-    <t>micro_0076_D15.jpg</t>
-  </si>
-  <si>
-    <t>micro_0020_D14.jpg</t>
-  </si>
-  <si>
-    <t>micro_0067_D13.jpg</t>
+    <t>micro_0064_D27.jpg</t>
+  </si>
+  <si>
+    <t>micro_0044_D26.jpg</t>
+  </si>
+  <si>
+    <t>micro_0065_D25.jpg</t>
+  </si>
+  <si>
+    <t>micro_0043_D24.jpg</t>
+  </si>
+  <si>
+    <t>micro_0089_D23.jpg</t>
+  </si>
+  <si>
+    <t>micro_0020_D22.jpg</t>
+  </si>
+  <si>
+    <t>micro_0035_D21.jpg</t>
+  </si>
+  <si>
+    <t>micro_0027_D20.jpg</t>
+  </si>
+  <si>
+    <t>micro_0082_D2.jpg</t>
+  </si>
+  <si>
+    <t>micro_0037_D19.jpg</t>
+  </si>
+  <si>
+    <t>micro_0025_D18.jpg</t>
+  </si>
+  <si>
+    <t>micro_0038_D17.jpg</t>
+  </si>
+  <si>
+    <t>micro_0024_D16.jpg</t>
+  </si>
+  <si>
+    <t>micro_0088_D15.jpg</t>
+  </si>
+  <si>
+    <t>micro_0023_D14.jpg</t>
+  </si>
+  <si>
+    <t>micro_0074_D13.jpg</t>
   </si>
   <si>
     <t>micro_0007_D12.jpg</t>
   </si>
   <si>
-    <t>micro_0065_D11.jpg</t>
-  </si>
-  <si>
-    <t>micro_0045_D10.jpg</t>
-  </si>
-  <si>
-    <t>micro_0016_D1H.jpg</t>
+    <t>micro_0076_D11.jpg</t>
+  </si>
+  <si>
+    <t>micro_0050_D10.jpg</t>
+  </si>
+  <si>
+    <t>micro_0018_D1H.jpg</t>
   </si>
   <si>
     <t>XⅡ</t>
@@ -754,7 +754,7 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>0.9085338115692139</v>
+        <v>0.8223272562026978</v>
       </c>
       <c r="D2" t="s">
         <v>114</v>
@@ -1054,7 +1054,7 @@
         <v>71</v>
       </c>
       <c r="C8">
-        <v>0.9273802042007446</v>
+        <v>0.9938356280326843</v>
       </c>
       <c r="D8" t="s">
         <v>114</v>
@@ -1354,7 +1354,7 @@
         <v>77</v>
       </c>
       <c r="C14">
-        <v>0.9960644245147705</v>
+        <v>0.9976902604103088</v>
       </c>
       <c r="D14" t="s">
         <v>114</v>
@@ -1654,7 +1654,7 @@
         <v>83</v>
       </c>
       <c r="C20">
-        <v>0.9721031785011292</v>
+        <v>0.9361289143562317</v>
       </c>
       <c r="D20" t="s">
         <v>114</v>
@@ -1754,7 +1754,7 @@
         <v>85</v>
       </c>
       <c r="C22">
-        <v>0.9989868402481079</v>
+        <v>0.9990725517272949</v>
       </c>
       <c r="D22" t="s">
         <v>114</v>
@@ -1804,7 +1804,7 @@
         <v>86</v>
       </c>
       <c r="C23">
-        <v>0.9908839464187622</v>
+        <v>0.9977337718009949</v>
       </c>
       <c r="D23" t="s">
         <v>114</v>
@@ -1904,7 +1904,7 @@
         <v>88</v>
       </c>
       <c r="C25">
-        <v>0.7785727977752686</v>
+        <v>0.9987778663635254</v>
       </c>
       <c r="D25" t="s">
         <v>114</v>
@@ -1937,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>91</v>
       </c>
       <c r="C28">
-        <v>0.9985227584838867</v>
+        <v>0.9975913166999817</v>
       </c>
       <c r="D28" t="s">
         <v>114</v>
@@ -2104,7 +2104,7 @@
         <v>92</v>
       </c>
       <c r="C29">
-        <v>0.9956930875778198</v>
+        <v>0.9990019202232361</v>
       </c>
       <c r="D29" t="s">
         <v>114</v>
@@ -2454,7 +2454,7 @@
         <v>99</v>
       </c>
       <c r="C36">
-        <v>0.9991309642791748</v>
+        <v>0.999164342880249</v>
       </c>
       <c r="D36" t="s">
         <v>114</v>
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>101</v>
       </c>
       <c r="C38">
-        <v>0.9898638129234314</v>
+        <v>0.9882310032844543</v>
       </c>
       <c r="D38" t="s">
         <v>114</v>
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -2654,7 +2654,7 @@
         <v>103</v>
       </c>
       <c r="C40">
-        <v>0.981236457824707</v>
+        <v>0.9835770726203918</v>
       </c>
       <c r="D40" t="s">
         <v>114</v>
@@ -2954,7 +2954,7 @@
         <v>109</v>
       </c>
       <c r="C46">
-        <v>0.9988886713981628</v>
+        <v>0.9990894794464111</v>
       </c>
       <c r="D46" t="s">
         <v>114</v>

--- a/template/t2_ocr_report.xlsx
+++ b/template/t2_ocr_report.xlsx
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1937,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -2225,19 +2225,19 @@
         <v>115</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2287,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -2387,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -2637,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="N42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -2887,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -3137,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
